--- a/TestDatas/api_test_data.xlsx
+++ b/TestDatas/api_test_data.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>是否鉴权</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -598,6 +603,11 @@
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>登录获取Token，提取用户名存入全局变量</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -657,6 +667,11 @@
           <t>验证GET请求基本功能</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -714,6 +729,11 @@
           <t>验证多个查询参数正确传递</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -771,6 +791,11 @@
           <t>验证POST请求体被正确回显</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -832,6 +857,11 @@
           <t>使用#login_token#引用全局变量</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -899,6 +929,11 @@
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>鉴权+数据双重验证，提取target存全局变量</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -958,6 +993,11 @@
           <t>验证PUT请求体正确回显</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1007,6 +1047,11 @@
           <t>验证DELETE请求</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1064,6 +1109,11 @@
           <t>验证PATCH请求体正确回显</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1125,6 +1175,11 @@
           <t>验证自定义请求头在响应中正确回显</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1174,6 +1229,11 @@
           <t>验证请求不存在的资源返回404</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1225,6 +1285,11 @@
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>此用例已禁用</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
